--- a/visium-hd/v2.0.0/visium-hd-v2.0.0.xlsx
+++ b/visium-hd/v2.0.0/visium-hd-v2.0.0.xlsx
@@ -99,13 +99,14 @@
     </comment>
     <comment ref="I1" authorId="1">
       <text>
-        <t>(Required) For assays where spots are used to define discrete capture areas,
-this is the area of a spot.</t>
+        <t>(Required) The area of a spot used in assays where spots define discrete capture
+areas.  Example: 2375.9</t>
       </text>
     </comment>
     <comment ref="J1" authorId="1">
       <text>
-        <t>(Required) The unit for spot size value.</t>
+        <t>(Required) The unit of measurement for the spot size value. If no spot size
+value is specified, this field may be left blank. Example: um^2</t>
       </text>
     </comment>
     <comment ref="K1" authorId="1">
@@ -117,8 +118,8 @@
     </comment>
     <comment ref="L1" authorId="1">
       <text>
-        <t>(Required) Approximate center-to-center distance between capture spots. 
-Synonyms: Inter-Spot distance, Spot resolution, Pit size</t>
+        <t>(Required) The approximate center-to-center distance between capture spots, also
+known as inter-spot distance, spot resolution, or pit size. Example: 100</t>
       </text>
     </comment>
     <comment ref="M1" authorId="1">
@@ -128,8 +129,9 @@
     </comment>
     <comment ref="N1" authorId="1">
       <text>
-        <t>(Required) Which capture area on the slide was used. For Visium this would be
-[A1, B1, C1, D1]. For HiFi this would be the lane on the flowcell.</t>
+        <t>(Required) The capture area on the slide that was used during the process. For
+example, in the case for Visium, this would correspond to areas such as [A1, B1,
+C1, D1], while for HiFi, it would refer to the lane on the flowcell. Example: A1</t>
       </text>
     </comment>
     <comment ref="O1" authorId="1">
@@ -186,7 +188,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="222">
   <si>
     <t>parent_sample_id</t>
   </si>
@@ -254,6 +256,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000217</t>
   </si>
   <si>
+    <t>Virtual Histology</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000473</t>
+  </si>
+  <si>
     <t>DBiT-seq</t>
   </si>
   <si>
@@ -284,6 +292,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000168</t>
   </si>
   <si>
+    <t>iCLAP</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000479</t>
+  </si>
+  <si>
     <t>seqFISH</t>
   </si>
   <si>
@@ -350,6 +364,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000207</t>
   </si>
   <si>
+    <t>MACSima</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000480</t>
+  </si>
+  <si>
     <t>CyTOF</t>
   </si>
   <si>
@@ -386,6 +406,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000219</t>
   </si>
   <si>
+    <t>DNA Methylation</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000490</t>
+  </si>
+  <si>
     <t>SIMS</t>
   </si>
   <si>
@@ -446,6 +472,12 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000209</t>
   </si>
   <si>
+    <t>Illumina Spatial ver0</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000487</t>
+  </si>
+  <si>
     <t>DART-FISH</t>
   </si>
   <si>
@@ -482,18 +514,36 @@
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000301</t>
   </si>
   <si>
+    <t>Raman Imaging</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000475</t>
+  </si>
+  <si>
     <t>RNAseq (with probes)</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000311</t>
   </si>
   <si>
+    <t>Paired-Tag</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000492</t>
+  </si>
+  <si>
     <t>MS Lipidomics</t>
   </si>
   <si>
     <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000405</t>
   </si>
   <si>
+    <t>STARmap</t>
+  </si>
+  <si>
+    <t>https://purl.humanatlas.io/vocab/hravs#HRAVS_0000476</t>
+  </si>
+  <si>
     <t>MPLEx</t>
   </si>
   <si>
@@ -647,6 +697,18 @@
     <t>https://identifiers.org/RRID:SCR_017105</t>
   </si>
   <si>
+    <t>Ionpath</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023605</t>
+  </si>
+  <si>
+    <t>Akoya Biosciences</t>
+  </si>
+  <si>
+    <t>https://identifiers.org/RRID:SCR_023774</t>
+  </si>
+  <si>
     <t>SunChrom</t>
   </si>
   <si>
@@ -680,6 +742,12 @@
     <t>https://identifiers.org/RRID:SCR_019326</t>
   </si>
   <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl#C65167</t>
+  </si>
+  <si>
     <t>NanoZoomer S360</t>
   </si>
   <si>
@@ -779,7 +847,7 @@
     <t>pav:createdOn</t>
   </si>
   <si>
-    <t>2025-10-21T13:33:45-07:00</t>
+    <t>2026-06-29T15:40:22-07:00</t>
   </si>
   <si>
     <t>pav:derivedFrom</t>
@@ -912,66 +980,66 @@
         <v>3</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>112</v>
+        <v>128</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>191</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2">
       <c r="D2" t="s" s="5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="T2" t="s" s="21">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D2:D1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'dataset_type'!$A$1:$A$50</formula1>
+      <formula1>'dataset_type'!$A$1:$A$58</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="G2:G1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="Value should be a number" showErrorMessage="true">
       <formula1>-3.4028235E38</formula1>
@@ -1009,10 +1077,10 @@
       <formula1>'permeabilization_time_unit'!$A$1:$A$1</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="Q2:Q1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_vendor'!$A$1:$A$9</formula1>
+      <formula1>'preparation_instrument_vendor'!$A$1:$A$11</formula1>
     </dataValidation>
     <dataValidation type="list" sqref="R2:R1001" allowBlank="true" errorStyle="stop" errorTitle="Validation Error" error="" showErrorMessage="true">
-      <formula1>'preparation_instrument_model'!$A$1:$A$18</formula1>
+      <formula1>'preparation_instrument_model'!$A$1:$A$19</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -1034,30 +1102,30 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="D1" t="s" s="0">
-        <v>198</v>
+        <v>220</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>199</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -1067,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B50"/>
+  <dimension ref="A1:B58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1468,6 +1536,70 @@
       </c>
       <c r="B50" t="s" s="0">
         <v>103</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1482,18 +1614,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1508,18 +1640,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>109</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>111</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1534,10 +1666,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>117</v>
+        <v>133</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>
@@ -1552,62 +1684,62 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>130</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>131</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>
@@ -1622,10 +1754,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>135</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -1635,79 +1767,95 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>140</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>144</v>
+        <v>160</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>146</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>148</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>150</v>
+        <v>166</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>152</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>154</v>
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -1717,151 +1865,159 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>157</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>142</v>
+        <v>158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="0">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s" s="0">
-        <v>159</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s" s="0">
-        <v>161</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>163</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="0">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>165</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>167</v>
+        <v>187</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="0">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>169</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="0">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>171</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="0">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s" s="0">
-        <v>173</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="0">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="B11" t="s" s="0">
-        <v>175</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="0">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>177</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="0">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>179</v>
+        <v>199</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="0">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>181</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="0">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="0">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>185</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="0">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>187</v>
+        <v>207</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="0">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>189</v>
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>211</v>
       </c>
     </row>
   </sheetData>
